--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/126.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/126.xlsx
@@ -426,13 +426,13 @@
         <v>-29.33658195729712</v>
       </c>
       <c r="E2">
-        <v>-7.689658877964391</v>
+        <v>-7.080819133055134</v>
       </c>
       <c r="F2">
-        <v>-1.692259306883701</v>
+        <v>-2.333691876754985</v>
       </c>
       <c r="G2">
-        <v>-13.29704897897542</v>
+        <v>-12.22618019229629</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-28.39606229903386</v>
       </c>
       <c r="E3">
-        <v>-7.619363375943323</v>
+        <v>-8.010650701050089</v>
       </c>
       <c r="F3">
-        <v>-1.321789316908612</v>
+        <v>-2.561191231507862</v>
       </c>
       <c r="G3">
-        <v>-14.02608407545157</v>
+        <v>-11.94946824339631</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-27.18843657197503</v>
       </c>
       <c r="E4">
-        <v>-9.204120968823595</v>
+        <v>-8.108316299973515</v>
       </c>
       <c r="F4">
-        <v>-1.465328502554467</v>
+        <v>-1.913461055063832</v>
       </c>
       <c r="G4">
-        <v>-13.02669658805638</v>
+        <v>-11.51767047816363</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-25.83624018278948</v>
       </c>
       <c r="E5">
-        <v>-9.220224222394872</v>
+        <v>-8.08869442209828</v>
       </c>
       <c r="F5">
-        <v>-1.436565235718255</v>
+        <v>-2.140130547917019</v>
       </c>
       <c r="G5">
-        <v>-12.63639651115847</v>
+        <v>-11.99110497464373</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-24.36779000373643</v>
       </c>
       <c r="E6">
-        <v>-9.99135089031701</v>
+        <v>-9.965438962045122</v>
       </c>
       <c r="F6">
-        <v>-0.9869242033244339</v>
+        <v>-2.311182664578845</v>
       </c>
       <c r="G6">
-        <v>-12.23054018077151</v>
+        <v>-11.42536915798321</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.83844742474637</v>
       </c>
       <c r="E7">
-        <v>-10.87386896187983</v>
+        <v>-9.00558813985332</v>
       </c>
       <c r="F7">
-        <v>-0.9014468439504205</v>
+        <v>-2.021613915735108</v>
       </c>
       <c r="G7">
-        <v>-11.89561559910899</v>
+        <v>-11.27845376804144</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.31334593200952</v>
       </c>
       <c r="E8">
-        <v>-11.41455970144765</v>
+        <v>-11.43494236295617</v>
       </c>
       <c r="F8">
-        <v>-0.8466981304536789</v>
+        <v>-2.190203369698425</v>
       </c>
       <c r="G8">
-        <v>-12.2915800194246</v>
+        <v>-10.32080232825984</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.8757838883631</v>
       </c>
       <c r="E9">
-        <v>-12.32318895413869</v>
+        <v>-10.72642184819008</v>
       </c>
       <c r="F9">
-        <v>-0.8437920300988475</v>
+        <v>-1.318930727731244</v>
       </c>
       <c r="G9">
-        <v>-11.64006796784157</v>
+        <v>-9.948150769631781</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-18.56692189019424</v>
       </c>
       <c r="E10">
-        <v>-12.05247224948615</v>
+        <v>-11.66590812276939</v>
       </c>
       <c r="F10">
-        <v>-0.6545898517931276</v>
+        <v>-1.813587017065517</v>
       </c>
       <c r="G10">
-        <v>-10.91019199279845</v>
+        <v>-9.072677001771515</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.45408922282782</v>
       </c>
       <c r="E11">
-        <v>-13.78724460081852</v>
+        <v>-12.98060111125422</v>
       </c>
       <c r="F11">
-        <v>-0.3242810601276683</v>
+        <v>-1.843064535269591</v>
       </c>
       <c r="G11">
-        <v>-10.55617880555648</v>
+        <v>-8.952865048159751</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.56990345177061</v>
       </c>
       <c r="E12">
-        <v>-12.89696925328056</v>
+        <v>-12.55802203075445</v>
       </c>
       <c r="F12">
-        <v>0.02165574151134735</v>
+        <v>-1.376812011528725</v>
       </c>
       <c r="G12">
-        <v>-9.369182702450798</v>
+        <v>-8.79429653791974</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.8962039461691</v>
       </c>
       <c r="E13">
-        <v>-14.17693790307458</v>
+        <v>-13.60098846488304</v>
       </c>
       <c r="F13">
-        <v>-0.1493409454434384</v>
+        <v>-1.117034354660319</v>
       </c>
       <c r="G13">
-        <v>-9.347660845899997</v>
+        <v>-8.85216818449174</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.43058532923796</v>
       </c>
       <c r="E14">
-        <v>-15.28076249939225</v>
+        <v>-13.90655630549861</v>
       </c>
       <c r="F14">
-        <v>0.2139469382051319</v>
+        <v>-0.7384415370449423</v>
       </c>
       <c r="G14">
-        <v>-9.045268995251888</v>
+        <v>-6.825995134818359</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.1374908377863</v>
       </c>
       <c r="E15">
-        <v>-15.82484053751781</v>
+        <v>-14.26205962899676</v>
       </c>
       <c r="F15">
-        <v>0.4941243109703131</v>
+        <v>-0.4833191837149708</v>
       </c>
       <c r="G15">
-        <v>-8.045024076562031</v>
+        <v>-7.38702004517649</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.9563456581978</v>
       </c>
       <c r="E16">
-        <v>-17.83323687381565</v>
+        <v>-16.63729858770796</v>
       </c>
       <c r="F16">
-        <v>0.8747046795095668</v>
+        <v>-0.6229901676623643</v>
       </c>
       <c r="G16">
-        <v>-8.10063130998517</v>
+        <v>-7.187003504784803</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.86346833851332</v>
       </c>
       <c r="E17">
-        <v>-17.88938542303675</v>
+        <v>-17.17684815182585</v>
       </c>
       <c r="F17">
-        <v>0.9472051526124692</v>
+        <v>-0.2557414355192799</v>
       </c>
       <c r="G17">
-        <v>-7.066685037705531</v>
+        <v>-5.549485190876321</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-14.82026847254968</v>
       </c>
       <c r="E18">
-        <v>-19.23132623962574</v>
+        <v>-17.84553168074647</v>
       </c>
       <c r="F18">
-        <v>0.8443418696987617</v>
+        <v>0.02617643004696926</v>
       </c>
       <c r="G18">
-        <v>-6.240634404201045</v>
+        <v>-5.527476684131246</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.78358171160889</v>
       </c>
       <c r="E19">
-        <v>-20.3002544152403</v>
+        <v>-18.56719382708283</v>
       </c>
       <c r="F19">
-        <v>1.216587194005057</v>
+        <v>0.2517927584663884</v>
       </c>
       <c r="G19">
-        <v>-5.32627827898204</v>
+        <v>-4.97892259881955</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.74489290594829</v>
       </c>
       <c r="E20">
-        <v>-20.19405264281241</v>
+        <v>-19.64231695513988</v>
       </c>
       <c r="F20">
-        <v>1.435483858225267</v>
+        <v>0.706106515163714</v>
       </c>
       <c r="G20">
-        <v>-5.446974148252789</v>
+        <v>-4.468578830122121</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.68091935605114</v>
       </c>
       <c r="E21">
-        <v>-21.52102685280605</v>
+        <v>-19.31437845292641</v>
       </c>
       <c r="F21">
-        <v>1.578098159616505</v>
+        <v>0.5475609241161132</v>
       </c>
       <c r="G21">
-        <v>-6.207264105165192</v>
+        <v>-5.137590425425739</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.57011416825068</v>
       </c>
       <c r="E22">
-        <v>-22.56420612521299</v>
+        <v>-21.30879086148856</v>
       </c>
       <c r="F22">
-        <v>1.804417653462379</v>
+        <v>1.143629029892593</v>
       </c>
       <c r="G22">
-        <v>-4.527993190915422</v>
+        <v>-4.401911064052278</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.41725402315116</v>
       </c>
       <c r="E23">
-        <v>-22.05223496780181</v>
+        <v>-20.70730535836776</v>
       </c>
       <c r="F23">
-        <v>2.014605518853587</v>
+        <v>0.8720678091603601</v>
       </c>
       <c r="G23">
-        <v>-4.690103984882453</v>
+        <v>-4.968342095276039</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-14.21787800693511</v>
       </c>
       <c r="E24">
-        <v>-23.06693919564852</v>
+        <v>-21.7090943783446</v>
       </c>
       <c r="F24">
-        <v>1.40704208368989</v>
+        <v>0.4676257435931803</v>
       </c>
       <c r="G24">
-        <v>-4.147879662641843</v>
+        <v>-3.885995647212257</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.97704087767602</v>
       </c>
       <c r="E25">
-        <v>-23.84363135812609</v>
+        <v>-22.7900954656636</v>
       </c>
       <c r="F25">
-        <v>1.503255385464667</v>
+        <v>0.6106217181100388</v>
       </c>
       <c r="G25">
-        <v>-4.44001544320929</v>
+        <v>-3.206658460371652</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.71869849014342</v>
       </c>
       <c r="E26">
-        <v>-23.00881623176008</v>
+        <v>-21.60596291129391</v>
       </c>
       <c r="F26">
-        <v>1.5553054640815</v>
+        <v>0.505677445623444</v>
       </c>
       <c r="G26">
-        <v>-4.070806851942071</v>
+        <v>-3.076193171214514</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-13.45271496516344</v>
       </c>
       <c r="E27">
-        <v>-24.43848264682565</v>
+        <v>-22.88728557481623</v>
       </c>
       <c r="F27">
-        <v>1.144729705503823</v>
+        <v>0.756297323035821</v>
       </c>
       <c r="G27">
-        <v>-3.773612557790618</v>
+        <v>-3.239101806656509</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-13.19534079715689</v>
       </c>
       <c r="E28">
-        <v>-24.32283900609178</v>
+        <v>-22.20647026402906</v>
       </c>
       <c r="F28">
-        <v>1.066922233878283</v>
+        <v>0.3730270299991935</v>
       </c>
       <c r="G28">
-        <v>-4.58936739466797</v>
+        <v>-4.354080302100888</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.96887851376026</v>
       </c>
       <c r="E29">
-        <v>-23.28990767036419</v>
+        <v>-22.71840066517417</v>
       </c>
       <c r="F29">
-        <v>1.090098186244824</v>
+        <v>0.2682237073390726</v>
       </c>
       <c r="G29">
-        <v>-4.438416449713822</v>
+        <v>-3.823376678336942</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.7747565716125</v>
       </c>
       <c r="E30">
-        <v>-23.45615700813378</v>
+        <v>-21.81464857898938</v>
       </c>
       <c r="F30">
-        <v>0.9820150086338283</v>
+        <v>0.4874529498015245</v>
       </c>
       <c r="G30">
-        <v>-4.130724415657339</v>
+        <v>-3.642385843159447</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-12.62057130641563</v>
       </c>
       <c r="E31">
-        <v>-22.45193166914082</v>
+        <v>-21.58185331567708</v>
       </c>
       <c r="F31">
-        <v>0.9219371247316328</v>
+        <v>0.4251143257050392</v>
       </c>
       <c r="G31">
-        <v>-4.275871974281146</v>
+        <v>-3.948061754982513</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.51368809386418</v>
       </c>
       <c r="E32">
-        <v>-22.25012928193701</v>
+        <v>-19.72902364696474</v>
       </c>
       <c r="F32">
-        <v>0.7243666443687309</v>
+        <v>0.4067290837327027</v>
       </c>
       <c r="G32">
-        <v>-4.331091873876189</v>
+        <v>-3.772202265390888</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.442103339005</v>
       </c>
       <c r="E33">
-        <v>-22.38222486874075</v>
+        <v>-20.86589251811638</v>
       </c>
       <c r="F33">
-        <v>1.050348751473209</v>
+        <v>0.6503141394686978</v>
       </c>
       <c r="G33">
-        <v>-4.223164778750409</v>
+        <v>-3.446484310873074</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-12.40686070487993</v>
       </c>
       <c r="E34">
-        <v>-21.80076427768187</v>
+        <v>-21.44598098155094</v>
       </c>
       <c r="F34">
-        <v>0.7908442838752171</v>
+        <v>0.2991748638974635</v>
       </c>
       <c r="G34">
-        <v>-4.489160491739771</v>
+        <v>-4.575585593587984</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-12.40544457018496</v>
       </c>
       <c r="E35">
-        <v>-21.57784108770628</v>
+        <v>-20.46123713773897</v>
       </c>
       <c r="F35">
-        <v>1.183467152195472</v>
+        <v>0.3651971879532609</v>
       </c>
       <c r="G35">
-        <v>-4.089269764414586</v>
+        <v>-5.076070557669463</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-12.41817499067007</v>
       </c>
       <c r="E36">
-        <v>-21.03394418854102</v>
+        <v>-20.50278588675934</v>
       </c>
       <c r="F36">
-        <v>1.199308962467613</v>
+        <v>0.2441727574542515</v>
       </c>
       <c r="G36">
-        <v>-4.423601758425583</v>
+        <v>-3.822671532137077</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-12.4447101433573</v>
       </c>
       <c r="E37">
-        <v>-19.59773865700837</v>
+        <v>-17.88023337706725</v>
       </c>
       <c r="F37">
-        <v>1.173163561509623</v>
+        <v>0.2882346234336078</v>
       </c>
       <c r="G37">
-        <v>-4.242183862873522</v>
+        <v>-4.036930039438708</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-12.47888371385258</v>
       </c>
       <c r="E38">
-        <v>-18.5896731720569</v>
+        <v>-19.09668112195568</v>
       </c>
       <c r="F38">
-        <v>1.495165815648603</v>
+        <v>0.3743042888199954</v>
       </c>
       <c r="G38">
-        <v>-3.915257559233875</v>
+        <v>-4.444054308767201</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-12.50202256273125</v>
       </c>
       <c r="E39">
-        <v>-18.91549687690878</v>
+        <v>-17.92982016745124</v>
       </c>
       <c r="F39">
-        <v>1.370460060749154</v>
+        <v>0.5477390910316002</v>
       </c>
       <c r="G39">
-        <v>-4.413203334886732</v>
+        <v>-3.213504668546864</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.52200539318125</v>
       </c>
       <c r="E40">
-        <v>-19.56898284705966</v>
+        <v>-17.88884653462984</v>
       </c>
       <c r="F40">
-        <v>1.345785922586608</v>
+        <v>0.857017851845939</v>
       </c>
       <c r="G40">
-        <v>-4.3594764913299</v>
+        <v>-3.927920395921587</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.53980805721219</v>
       </c>
       <c r="E41">
-        <v>-17.67929139992489</v>
+        <v>-17.98956885350844</v>
       </c>
       <c r="F41">
-        <v>1.668358310855145</v>
+        <v>0.5824855988163417</v>
       </c>
       <c r="G41">
-        <v>-4.925291761083357</v>
+        <v>-4.558178745142496</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.54751114074249</v>
       </c>
       <c r="E42">
-        <v>-17.46941021509139</v>
+        <v>-18.08271050689821</v>
       </c>
       <c r="F42">
-        <v>1.178381872500996</v>
+        <v>0.603583729021826</v>
       </c>
       <c r="G42">
-        <v>-4.92396092177657</v>
+        <v>-4.374208418979657</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.56262016142938</v>
       </c>
       <c r="E43">
-        <v>-17.32357976662239</v>
+        <v>-16.76309053869302</v>
       </c>
       <c r="F43">
-        <v>1.382244416465939</v>
+        <v>0.3651267130400238</v>
       </c>
       <c r="G43">
-        <v>-5.13317746822189</v>
+        <v>-4.740748710542223</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.59043480630797</v>
       </c>
       <c r="E44">
-        <v>-16.23723055150032</v>
+        <v>-16.33981407319608</v>
       </c>
       <c r="F44">
-        <v>1.471665203569397</v>
+        <v>0.8719078548629007</v>
       </c>
       <c r="G44">
-        <v>-4.312513092309799</v>
+        <v>-4.223730882037624</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.62809507407798</v>
       </c>
       <c r="E45">
-        <v>-14.59040569387092</v>
+        <v>-15.6709765761592</v>
       </c>
       <c r="F45">
-        <v>1.514287480871618</v>
+        <v>0.8771594236784979</v>
       </c>
       <c r="G45">
-        <v>-4.977128283137265</v>
+        <v>-4.439174564642315</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-12.69070630250655</v>
       </c>
       <c r="E46">
-        <v>-14.78513007620074</v>
+        <v>-14.74494439785668</v>
       </c>
       <c r="F46">
-        <v>1.57379364693834</v>
+        <v>0.7230204943406073</v>
       </c>
       <c r="G46">
-        <v>-4.89125273184857</v>
+        <v>-4.926698742937547</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-12.77393099186817</v>
       </c>
       <c r="E47">
-        <v>-13.91992888924326</v>
+        <v>-14.70825017297252</v>
       </c>
       <c r="F47">
-        <v>1.407609050407617</v>
+        <v>0.4923141351089659</v>
       </c>
       <c r="G47">
-        <v>-6.198689792218479</v>
+        <v>-4.876639983838227</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-12.86805562013854</v>
       </c>
       <c r="E48">
-        <v>-13.45771660422836</v>
+        <v>-14.76666295919746</v>
       </c>
       <c r="F48">
-        <v>1.597205571486282</v>
+        <v>0.231474603424258</v>
       </c>
       <c r="G48">
-        <v>-6.070353183843093</v>
+        <v>-4.711596046523401</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.98003538668523</v>
       </c>
       <c r="E49">
-        <v>-12.63231617532429</v>
+        <v>-12.09113636056364</v>
       </c>
       <c r="F49">
-        <v>1.402062912291748</v>
+        <v>0.4991216949864823</v>
       </c>
       <c r="G49">
-        <v>-5.295414062919415</v>
+        <v>-5.674915140268228</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.10219657583607</v>
       </c>
       <c r="E50">
-        <v>-12.89969992310719</v>
+        <v>-12.75602955673984</v>
       </c>
       <c r="F50">
-        <v>1.284265282595447</v>
+        <v>0.06490675006199866</v>
       </c>
       <c r="G50">
-        <v>-6.548064905159925</v>
+        <v>-5.96557110697962</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.2315637275443</v>
       </c>
       <c r="E51">
-        <v>-12.01389870788882</v>
+        <v>-11.57776590468409</v>
       </c>
       <c r="F51">
-        <v>1.418120106568389</v>
+        <v>0.457269098759164</v>
       </c>
       <c r="G51">
-        <v>-5.009161121775253</v>
+        <v>-5.498578932118948</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.37912895574874</v>
       </c>
       <c r="E52">
-        <v>-12.16826080138827</v>
+        <v>-11.48138186390483</v>
       </c>
       <c r="F52">
-        <v>1.281036106233866</v>
+        <v>0.5936317210492045</v>
       </c>
       <c r="G52">
-        <v>-5.478106518504095</v>
+        <v>-4.86599989047501</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.53980685702355</v>
       </c>
       <c r="E53">
-        <v>-12.24243720563391</v>
+        <v>-11.96550743464285</v>
       </c>
       <c r="F53">
-        <v>0.9962303529308127</v>
+        <v>0.4518702452934309</v>
       </c>
       <c r="G53">
-        <v>-5.975092235950564</v>
+        <v>-4.230047402926554</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.71612401112447</v>
       </c>
       <c r="E54">
-        <v>-10.89895217940831</v>
+        <v>-10.51896339695068</v>
       </c>
       <c r="F54">
-        <v>1.016273734996614</v>
+        <v>0.5321585922355069</v>
       </c>
       <c r="G54">
-        <v>-6.201768599570002</v>
+        <v>-6.316194295589371</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-13.91658308172819</v>
       </c>
       <c r="E55">
-        <v>-10.52499985280291</v>
+        <v>-10.12143583466135</v>
       </c>
       <c r="F55">
-        <v>1.177358798479622</v>
+        <v>0.311898357222104</v>
       </c>
       <c r="G55">
-        <v>-7.072114332389936</v>
+        <v>-5.43556931887</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.13020180022106</v>
       </c>
       <c r="E56">
-        <v>-10.38250688967755</v>
+        <v>-11.3145211821442</v>
       </c>
       <c r="F56">
-        <v>0.8562529218887818</v>
+        <v>0.2888760243293608</v>
       </c>
       <c r="G56">
-        <v>-6.886670813462121</v>
+        <v>-5.562081816653248</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.35638067131168</v>
       </c>
       <c r="E57">
-        <v>-10.60008195185008</v>
+        <v>-8.83081621400129</v>
       </c>
       <c r="F57">
-        <v>1.554155693586891</v>
+        <v>0.2062596296915888</v>
       </c>
       <c r="G57">
-        <v>-7.20164273715946</v>
+        <v>-5.957046452215997</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.59398632720846</v>
       </c>
       <c r="E58">
-        <v>-9.17693653935555</v>
+        <v>-9.405216914082214</v>
       </c>
       <c r="F58">
-        <v>0.6798930148513603</v>
+        <v>0.311401073564656</v>
       </c>
       <c r="G58">
-        <v>-7.367554037405576</v>
+        <v>-6.60450639605896</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.82439410595199</v>
       </c>
       <c r="E59">
-        <v>-9.185259874581648</v>
+        <v>-9.398745724725252</v>
       </c>
       <c r="F59">
-        <v>0.9779781422553732</v>
+        <v>0.1463187363510789</v>
       </c>
       <c r="G59">
-        <v>-7.070793424719767</v>
+        <v>-5.786460661668431</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-15.04683657154699</v>
       </c>
       <c r="E60">
-        <v>-9.536148683065987</v>
+        <v>-8.137063052974206</v>
       </c>
       <c r="F60">
-        <v>0.5707582565125126</v>
+        <v>-0.009077655483670564</v>
       </c>
       <c r="G60">
-        <v>-7.28431368036614</v>
+        <v>-6.897648582470344</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.25758584758236</v>
       </c>
       <c r="E61">
-        <v>-9.466265272179617</v>
+        <v>-7.60164345715131</v>
       </c>
       <c r="F61">
-        <v>0.9008865057036117</v>
+        <v>0.003045613299018405</v>
       </c>
       <c r="G61">
-        <v>-6.938318634420291</v>
+        <v>-6.443074263927478</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.43718786796857</v>
       </c>
       <c r="E62">
-        <v>-9.095894968514282</v>
+        <v>-8.365008320624302</v>
       </c>
       <c r="F62">
-        <v>0.3797332326981219</v>
+        <v>-0.1929237403833743</v>
       </c>
       <c r="G62">
-        <v>-7.770629509539539</v>
+        <v>-6.6016858112595</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-15.58976118938959</v>
       </c>
       <c r="E63">
-        <v>-7.073510176006754</v>
+        <v>-8.725923170561622</v>
       </c>
       <c r="F63">
-        <v>0.7395955604515966</v>
+        <v>-0.1339172335329736</v>
       </c>
       <c r="G63">
-        <v>-7.250413694044004</v>
+        <v>-6.598835431550188</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-15.71260092902574</v>
       </c>
       <c r="E64">
-        <v>-8.481000653856769</v>
+        <v>-5.240542394292062</v>
       </c>
       <c r="F64">
-        <v>0.4608292696570719</v>
+        <v>0.07142369990403198</v>
       </c>
       <c r="G64">
-        <v>-7.482085670882201</v>
+        <v>-6.488144030899116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.78980749920334</v>
       </c>
       <c r="E65">
-        <v>-7.664756799396211</v>
+        <v>-7.37285136486178</v>
       </c>
       <c r="F65">
-        <v>0.5211296642403866</v>
+        <v>-0.4310267980930757</v>
       </c>
       <c r="G65">
-        <v>-7.296284613036145</v>
+        <v>-6.286376211917156</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.8321673813927</v>
       </c>
       <c r="E66">
-        <v>-7.722028410171218</v>
+        <v>-5.928005504922491</v>
       </c>
       <c r="F66">
-        <v>0.2165386729357485</v>
+        <v>-0.2276021488137518</v>
       </c>
       <c r="G66">
-        <v>-7.873193520891699</v>
+        <v>-7.320544290747924</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.83880464575797</v>
       </c>
       <c r="E67">
-        <v>-7.958369468631534</v>
+        <v>-7.82786790467849</v>
       </c>
       <c r="F67">
-        <v>0.4535038379452068</v>
+        <v>-0.6279930946492375</v>
       </c>
       <c r="G67">
-        <v>-7.366319203919427</v>
+        <v>-6.522375071775181</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.79847809010433</v>
       </c>
       <c r="E68">
-        <v>-7.947727554713508</v>
+        <v>-6.328177696032305</v>
       </c>
       <c r="F68">
-        <v>0.1580080697129375</v>
+        <v>-0.7735879305733322</v>
       </c>
       <c r="G68">
-        <v>-8.114982524897909</v>
+        <v>-8.093871175993977</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.7262602556816</v>
       </c>
       <c r="E69">
-        <v>-7.195502737299385</v>
+        <v>-7.36283890883082</v>
       </c>
       <c r="F69">
-        <v>0.4270488224807485</v>
+        <v>-0.2831126248558199</v>
       </c>
       <c r="G69">
-        <v>-8.400543562024364</v>
+        <v>-6.981968177355582</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.62235252885996</v>
       </c>
       <c r="E70">
-        <v>-7.548687482105612</v>
+        <v>-6.871381738674388</v>
       </c>
       <c r="F70">
-        <v>0.01681435252784896</v>
+        <v>-0.5177299458456391</v>
       </c>
       <c r="G70">
-        <v>-8.267072297517567</v>
+        <v>-6.750551112523908</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.4806126542941</v>
       </c>
       <c r="E71">
-        <v>-8.62832549874831</v>
+        <v>-7.224367230624277</v>
       </c>
       <c r="F71">
-        <v>0.1438822048001753</v>
+        <v>-0.6977189149882901</v>
       </c>
       <c r="G71">
-        <v>-8.054763701538567</v>
+        <v>-8.278112966891037</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.31585109595557</v>
       </c>
       <c r="E72">
-        <v>-8.103873866971991</v>
+        <v>-8.107202295367628</v>
       </c>
       <c r="F72">
-        <v>-0.2075674771304851</v>
+        <v>-0.9207886442956825</v>
       </c>
       <c r="G72">
-        <v>-7.618927070747976</v>
+        <v>-6.349700326992335</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.12492169769709</v>
       </c>
       <c r="E73">
-        <v>-7.182401861995196</v>
+        <v>-7.086606522836937</v>
       </c>
       <c r="F73">
-        <v>-0.01860839768278516</v>
+        <v>-0.3769274040216642</v>
       </c>
       <c r="G73">
-        <v>-7.868184665490782</v>
+        <v>-7.676451110038352</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.90279940985812</v>
       </c>
       <c r="E74">
-        <v>-8.130071089106364</v>
+        <v>-7.778933214551604</v>
       </c>
       <c r="F74">
-        <v>-0.1716213121147983</v>
+        <v>-0.8005053881650988</v>
       </c>
       <c r="G74">
-        <v>-8.148697120669848</v>
+        <v>-6.435635468100736</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.66075402725042</v>
       </c>
       <c r="E75">
-        <v>-9.2333477400691</v>
+        <v>-8.749801814004067</v>
       </c>
       <c r="F75">
-        <v>-0.09388510725545297</v>
+        <v>-0.7875110811289181</v>
       </c>
       <c r="G75">
-        <v>-7.559290903403545</v>
+        <v>-5.896099308838014</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.39467731296833</v>
       </c>
       <c r="E76">
-        <v>-8.585064986553036</v>
+        <v>-8.712582286135024</v>
       </c>
       <c r="F76">
-        <v>-0.5477372136784281</v>
+        <v>-0.997258676275634</v>
       </c>
       <c r="G76">
-        <v>-7.678930708647266</v>
+        <v>-8.003062911851769</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.10553426130449</v>
       </c>
       <c r="E77">
-        <v>-9.409487265071446</v>
+        <v>-9.156576520217065</v>
       </c>
       <c r="F77">
-        <v>-0.571526060234244</v>
+        <v>-0.6460742650858097</v>
       </c>
       <c r="G77">
-        <v>-7.399206163306547</v>
+        <v>-6.174006364677673</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.80721063774493</v>
       </c>
       <c r="E78">
-        <v>-9.136307070558733</v>
+        <v>-9.740314933701805</v>
       </c>
       <c r="F78">
-        <v>-0.1771120205236268</v>
+        <v>-0.7282242583314846</v>
       </c>
       <c r="G78">
-        <v>-7.409809840668832</v>
+        <v>-6.035450102222557</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.49891603574438</v>
       </c>
       <c r="E79">
-        <v>-9.874842311047669</v>
+        <v>-8.811257734762162</v>
       </c>
       <c r="F79">
-        <v>-0.3014701519746363</v>
+        <v>-1.017319479106505</v>
       </c>
       <c r="G79">
-        <v>-7.508225738460286</v>
+        <v>-6.438273972895535</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.19087013573373</v>
       </c>
       <c r="E80">
-        <v>-11.21831375185125</v>
+        <v>-10.31521829439758</v>
       </c>
       <c r="F80">
-        <v>-0.3387149558409835</v>
+        <v>-1.070809146400473</v>
       </c>
       <c r="G80">
-        <v>-7.015040527292901</v>
+        <v>-5.244391935068167</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.90059060839523</v>
       </c>
       <c r="E81">
-        <v>-11.3295149595836</v>
+        <v>-10.46435452889219</v>
       </c>
       <c r="F81">
-        <v>-0.7769247989371632</v>
+        <v>-1.355932432739571</v>
       </c>
       <c r="G81">
-        <v>-7.13955345557043</v>
+        <v>-6.510016805277081</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.62916478402975</v>
       </c>
       <c r="E82">
-        <v>-11.61721344176491</v>
+        <v>-11.11816202069761</v>
       </c>
       <c r="F82">
-        <v>-0.3939672878188349</v>
+        <v>-1.499370261206838</v>
       </c>
       <c r="G82">
-        <v>-7.228027785107452</v>
+        <v>-6.019619073453762</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.39001520860166</v>
       </c>
       <c r="E83">
-        <v>-13.38147521583523</v>
+        <v>-13.31125669787229</v>
       </c>
       <c r="F83">
-        <v>-0.2354541627425006</v>
+        <v>-1.501638128077747</v>
       </c>
       <c r="G83">
-        <v>-7.038320283525056</v>
+        <v>-6.101220710451257</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.19560876246727</v>
       </c>
       <c r="E84">
-        <v>-14.2423607670634</v>
+        <v>-11.68287631487613</v>
       </c>
       <c r="F84">
-        <v>-0.3546407025266425</v>
+        <v>-1.345042079012052</v>
       </c>
       <c r="G84">
-        <v>-6.553216114019031</v>
+        <v>-5.725374475377799</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.04041268010667</v>
       </c>
       <c r="E85">
-        <v>-14.75215372847689</v>
+        <v>-16.31778304714876</v>
       </c>
       <c r="F85">
-        <v>-0.6395240574195521</v>
+        <v>-0.7347570452326724</v>
       </c>
       <c r="G85">
-        <v>-6.387218739588895</v>
+        <v>-6.208651223746147</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-11.93456396958257</v>
       </c>
       <c r="E86">
-        <v>-16.23966234204244</v>
+        <v>-14.52247858375586</v>
       </c>
       <c r="F86">
-        <v>-0.3944170602988197</v>
+        <v>-1.321725968671995</v>
       </c>
       <c r="G86">
-        <v>-6.603016650566287</v>
+        <v>-5.073455226693438</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-11.88125750230915</v>
       </c>
       <c r="E87">
-        <v>-17.21130078207621</v>
+        <v>-17.20460769749287</v>
       </c>
       <c r="F87">
-        <v>-0.6288229565489277</v>
+        <v>-1.119731405834313</v>
       </c>
       <c r="G87">
-        <v>-5.969255744164829</v>
+        <v>-4.952103869405914</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-11.86535033142061</v>
       </c>
       <c r="E88">
-        <v>-18.32640580714698</v>
+        <v>-19.5473956114651</v>
       </c>
       <c r="F88">
-        <v>-0.1998556211752527</v>
+        <v>-1.041012511454437</v>
       </c>
       <c r="G88">
-        <v>-5.972579531886257</v>
+        <v>-6.469770503156162</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.88969760761817</v>
       </c>
       <c r="E89">
-        <v>-20.88684123887586</v>
+        <v>-19.77717943956231</v>
       </c>
       <c r="F89">
-        <v>-0.4979059070491259</v>
+        <v>-0.711209713828961</v>
       </c>
       <c r="G89">
-        <v>-6.161187932349615</v>
+        <v>-5.886147808946966</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.94360850680444</v>
       </c>
       <c r="E90">
-        <v>-21.25787722822032</v>
+        <v>-20.59769817348611</v>
       </c>
       <c r="F90">
-        <v>-0.2509982363025388</v>
+        <v>-1.452674692290105</v>
       </c>
       <c r="G90">
-        <v>-5.432440853335389</v>
+        <v>-4.960234569250364</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.9999931546132</v>
       </c>
       <c r="E91">
-        <v>-23.81180071432617</v>
+        <v>-23.5542301697179</v>
       </c>
       <c r="F91">
-        <v>-0.3099073452391399</v>
+        <v>-1.150844892249036</v>
       </c>
       <c r="G91">
-        <v>-6.466847291444985</v>
+        <v>-5.977730740745363</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.05023499259612</v>
       </c>
       <c r="E92">
-        <v>-25.75263674690358</v>
+        <v>-25.2281534158092</v>
       </c>
       <c r="F92">
-        <v>-0.5079363084645616</v>
+        <v>-1.326868261779427</v>
       </c>
       <c r="G92">
-        <v>-5.546270651157688</v>
+        <v>-4.460431577549975</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.07410522597289</v>
       </c>
       <c r="E93">
-        <v>-28.31744215604986</v>
+        <v>-27.88544837808815</v>
       </c>
       <c r="F93">
-        <v>-0.5381462906545268</v>
+        <v>-1.335897761056305</v>
       </c>
       <c r="G93">
-        <v>-5.594545026211342</v>
+        <v>-5.762919372338674</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.0462039016916</v>
       </c>
       <c r="E94">
-        <v>-30.82049955786455</v>
+        <v>-29.20332941227438</v>
       </c>
       <c r="F94">
-        <v>-0.4767309671067427</v>
+        <v>-1.593746464119705</v>
       </c>
       <c r="G94">
-        <v>-6.042081124937717</v>
+        <v>-5.431354994398507</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.9672604806404</v>
       </c>
       <c r="E95">
-        <v>-33.6412746960574</v>
+        <v>-32.24657489304204</v>
       </c>
       <c r="F95">
-        <v>-0.4952619100232997</v>
+        <v>-1.584357463600022</v>
       </c>
       <c r="G95">
-        <v>-5.619655514126713</v>
+        <v>-5.215739163425775</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.83539274078969</v>
       </c>
       <c r="E96">
-        <v>-34.80918625653162</v>
+        <v>-34.2559244731185</v>
       </c>
       <c r="F96">
-        <v>-0.7334338589403228</v>
+        <v>-1.51414544554493</v>
       </c>
       <c r="G96">
-        <v>-6.001828201725719</v>
+        <v>-5.912145523066862</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.65121972969081</v>
       </c>
       <c r="E97">
-        <v>-37.42612798692821</v>
+        <v>-36.76944038565391</v>
       </c>
       <c r="F97">
-        <v>-0.8962997997252423</v>
+        <v>-1.484862723168455</v>
       </c>
       <c r="G97">
-        <v>-6.105924995662561</v>
+        <v>-5.913631958013995</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.44194975441219</v>
       </c>
       <c r="E98">
-        <v>-40.8899803977653</v>
+        <v>-38.55487503994708</v>
       </c>
       <c r="F98">
-        <v>-0.5916985143321539</v>
+        <v>-1.183146158100339</v>
       </c>
       <c r="G98">
-        <v>-6.079967008089136</v>
+        <v>-5.859938219912555</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.21875006031507</v>
       </c>
       <c r="E99">
-        <v>-43.50939014649607</v>
+        <v>-42.79924390956123</v>
       </c>
       <c r="F99">
-        <v>-0.5499781575487749</v>
+        <v>-1.844063061849276</v>
       </c>
       <c r="G99">
-        <v>-6.786434115624068</v>
+        <v>-6.465486657228344</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.00504245945704</v>
       </c>
       <c r="E100">
-        <v>-44.9224959321156</v>
+        <v>-45.54760648413442</v>
       </c>
       <c r="F100">
-        <v>-0.5550246364483227</v>
+        <v>-1.976958160037461</v>
       </c>
       <c r="G100">
-        <v>-7.05787898657107</v>
+        <v>-5.598799077229304</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.81703722443046</v>
       </c>
       <c r="E101">
-        <v>-47.7866334731689</v>
+        <v>-47.54736022778862</v>
       </c>
       <c r="F101">
-        <v>-0.5292830804987699</v>
+        <v>-1.739270033277605</v>
       </c>
       <c r="G101">
-        <v>-7.092636404187878</v>
+        <v>-6.109271957202765</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.68813019929346</v>
       </c>
       <c r="E102">
-        <v>-50.92597883297184</v>
+        <v>-50.09734507362629</v>
       </c>
       <c r="F102">
-        <v>-1.008156156679773</v>
+        <v>-1.808601510843713</v>
       </c>
       <c r="G102">
-        <v>-6.739570032970145</v>
+        <v>-7.54005332327484</v>
       </c>
     </row>
   </sheetData>
